--- a/experiments/results/resnet_imagenet34/ImageNet-1K/ReAct/standard/results.xlsx
+++ b/experiments/results/resnet_imagenet34/ImageNet-1K/ReAct/standard/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -503,6 +503,154 @@
       <c r="K4" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=2.0,scale_th=None,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>61.64</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>65.92</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>83.12</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>88.33</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>66.45</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>83.39</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>70.59</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>77.15000000000001</v>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=None,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>91.59</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>84.23999999999999</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>94.73999999999999</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>38.74</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>91.18000000000001</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.5,scale_th=None,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>94.14</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>91.01000000000001</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>95.70999999999999</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=2.1,scale_th=None,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>94.39</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>34.04</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>90.09</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>95.73999999999999</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.9,scale_th=None,type=avg</t>
         </is>
       </c>
     </row>
